--- a/guide-bo-report/Guide BO Report.xlsx
+++ b/guide-bo-report/Guide BO Report.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\bo-report\guide-bo-report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271A46B5-B6B9-4B55-9049-AC4B17864219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A24187-DB9D-4841-A475-318EA7726707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{DC4FA598-7289-4AE5-ACE4-DD11C1AC9C34}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Template" sheetId="1" r:id="rId1"/>
     <sheet name="Guide" sheetId="3" r:id="rId2"/>
+    <sheet name="Estimasi &amp; Remark" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Guide!$A$1:$D$65</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="155">
   <si>
     <t>Customer Reference Number</t>
   </si>
@@ -349,13 +350,172 @@
   </si>
   <si>
     <t>Deletion indicator</t>
+  </si>
+  <si>
+    <t>MENGISI ESTIMASI DAN REMARK</t>
+  </si>
+  <si>
+    <t>PURCHASING DOCUMENT</t>
+  </si>
+  <si>
+    <t>BLANK</t>
+  </si>
+  <si>
+    <t>ESTIMASI</t>
+  </si>
+  <si>
+    <t>TBA</t>
+  </si>
+  <si>
+    <t>REMARK</t>
+  </si>
+  <si>
+    <t>Waiting for branch release or Caterpillar submit</t>
+  </si>
+  <si>
+    <t>CLASS</t>
+  </si>
+  <si>
+    <t>ASSY</t>
+  </si>
+  <si>
+    <t>PO Subcont BUILD UP</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>YANG ADA NO PO</t>
+  </si>
+  <si>
+    <t>SHIPMENT NUMBER</t>
+  </si>
+  <si>
+    <t>TODAY() + ETA</t>
+  </si>
+  <si>
+    <t>Follow Up Cabang</t>
+  </si>
+  <si>
+    <t>YANG ADA NO SHIPMENT</t>
+  </si>
+  <si>
+    <t>SHIPMENT NUMBER DATE + ETA</t>
+  </si>
+  <si>
+    <t>Follow Up CKB</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>VENDOR/SUPPLYING PLANT</t>
+  </si>
+  <si>
+    <t>1000085    CATERPILLAR ASIA DELIVERY CENTER</t>
+  </si>
+  <si>
+    <t>AGREEMENT TYPE</t>
+  </si>
+  <si>
+    <t>CPRO</t>
+  </si>
+  <si>
+    <t>MILESTONE</t>
+  </si>
+  <si>
+    <t>SOURCED</t>
+  </si>
+  <si>
+    <t>SHP BY DT + ETA</t>
+  </si>
+  <si>
+    <t>Waiting Inv</t>
+  </si>
+  <si>
+    <t>SHIPPED</t>
+  </si>
+  <si>
+    <t>ACT DEPT DT -INV CAT + ETA</t>
+  </si>
+  <si>
+    <t>FUTURE DATED</t>
+  </si>
+  <si>
+    <t>F/U ESD</t>
+  </si>
+  <si>
+    <t>ESD NEEDED</t>
+  </si>
+  <si>
+    <t>TODAY() + 120</t>
+  </si>
+  <si>
+    <t>ESD AVAILABLE</t>
+  </si>
+  <si>
+    <t>EST SHIP DATE + ETA</t>
+  </si>
+  <si>
+    <t>MEGA / DOWN</t>
+  </si>
+  <si>
+    <t>ESD Needed</t>
+  </si>
+  <si>
+    <t>SOURCE DATE + 3 + ETA</t>
+  </si>
+  <si>
+    <t>Waiting invoice</t>
+  </si>
+  <si>
+    <t>Waiting handover to CKB</t>
+  </si>
+  <si>
+    <t>SNSKI</t>
+  </si>
+  <si>
+    <t>SOH</t>
+  </si>
+  <si>
+    <t>Pre-Stock</t>
+  </si>
+  <si>
+    <t>Reserve</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>On-Order</t>
+  </si>
+  <si>
+    <t>Hazardous Indicator</t>
+  </si>
+  <si>
+    <t>Replacement Indicator</t>
+  </si>
+  <si>
+    <t>Deletion Indicator</t>
+  </si>
+  <si>
+    <t>Returnable Indicator</t>
+  </si>
+  <si>
+    <t>Package Qty</t>
+  </si>
+  <si>
+    <t>Commodity Code</t>
+  </si>
+  <si>
+    <t>VLOOKUP Material No &amp; plant 1G38 ke folder (kolom C)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -379,8 +539,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -435,8 +609,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -457,11 +643,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -515,6 +809,42 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -850,7 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B2821F-701F-4D9B-A36C-377D99F41020}">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.140625" style="9" bestFit="1" customWidth="1"/>
@@ -919,7 +1249,7 @@
     <col min="68" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:80" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,6 +1452,42 @@
         <v>101</v>
       </c>
       <c r="BP1" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="BQ1" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="BR1" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="BS1" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="BT1" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="BU1" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="BV1" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="BW1" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="BX1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="BY1" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="BZ1" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="CA1" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="CB1" s="21" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1132,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4E3129-3060-4477-BF24-93273BE0A18F}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
@@ -1855,11 +2221,11 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
         <v>58</v>
@@ -1877,12 +2243,949 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="19" t="s">
+      <c r="A69" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C74" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="19" t="s">
         <v>66</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C81" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D65" xr:uid="{6C4E3129-3060-4477-BF24-93273BE0A18F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1319D52C-8C14-42CD-85EC-1D0FF8B6A656}">
+  <dimension ref="A1:B108"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="31"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+    </row>
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="26"/>
+      <c r="B35" s="27"/>
+    </row>
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="26"/>
+      <c r="B42" s="27"/>
+    </row>
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="26"/>
+      <c r="B43" s="27"/>
+    </row>
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="26"/>
+      <c r="B44" s="27"/>
+    </row>
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="26"/>
+      <c r="B51" s="27"/>
+    </row>
+    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="26"/>
+      <c r="B58" s="27"/>
+    </row>
+    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="26"/>
+      <c r="B65" s="27"/>
+    </row>
+    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="26"/>
+      <c r="B72" s="27"/>
+    </row>
+    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B74" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B76" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B77" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="26"/>
+      <c r="B79" s="27"/>
+    </row>
+    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B80" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B82" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B83" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" s="23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="26"/>
+      <c r="B86" s="27"/>
+    </row>
+    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="26"/>
+      <c r="B87" s="27"/>
+    </row>
+    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" s="26"/>
+      <c r="B88" s="27"/>
+    </row>
+    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A91" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B91" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A92" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B92" s="23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A93" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B93" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A94" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B94" s="23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A95" s="26"/>
+      <c r="B95" s="27"/>
+    </row>
+    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A96" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B96" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A97" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B97" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A98" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A99" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A101" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A102" s="26"/>
+      <c r="B102" s="27"/>
+    </row>
+    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A103" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A104" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A105" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B105" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A106" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B106" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A107" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>